--- a/res/hERV_DE/hERV_group_celltype.xlsx
+++ b/res/hERV_DE/hERV_group_celltype.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17185\Desktop\hERV_AD_snRNA-seq_analyze\res\hERV_DE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C2C6B7-133B-43E2-A86B-0F7B98D1FEF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{376D46EA-DF05-4E22-B20A-D8E9DFA5D709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1160" windowWidth="12820" windowHeight="14840" xr2:uid="{B6C39286-441A-499E-BB16-069EE71EE863}"/>
+    <workbookView xWindow="0" yWindow="10" windowWidth="12820" windowHeight="11400" xr2:uid="{B6C39286-441A-499E-BB16-069EE71EE863}"/>
   </bookViews>
   <sheets>
     <sheet name="hERV_group_celltype" sheetId="1" r:id="rId1"/>
@@ -22,16 +22,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="35">
   <si>
-    <t>celltype</t>
-  </si>
-  <si>
     <t>n_NC</t>
   </si>
   <si>
     <t>n_AD</t>
-  </si>
-  <si>
-    <t>subfamily</t>
   </si>
   <si>
     <t>p_val</t>
@@ -125,6 +119,14 @@
   </si>
   <si>
     <t>All</t>
+  </si>
+  <si>
+    <t>celltype</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>feature</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1090,36 +1092,36 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>26896</v>
@@ -1128,7 +1130,7 @@
         <v>31494</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1">
         <v>1.43229724169776E-60</v>
@@ -1148,7 +1150,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>26896</v>
@@ -1157,7 +1159,7 @@
         <v>31494</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1">
         <v>1.22364723433083E-57</v>
@@ -1177,7 +1179,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>26896</v>
@@ -1186,7 +1188,7 @@
         <v>31494</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E4" s="1">
         <v>8.7495715407912102E-24</v>
@@ -1206,7 +1208,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>26896</v>
@@ -1215,7 +1217,7 @@
         <v>31494</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E5" s="1">
         <v>2.98167590122043E-21</v>
@@ -1235,7 +1237,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>26896</v>
@@ -1244,7 +1246,7 @@
         <v>31494</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1">
         <v>4.2151092171651003E-21</v>
@@ -1264,7 +1266,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7">
         <v>26896</v>
@@ -1273,7 +1275,7 @@
         <v>31494</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E7" s="1">
         <v>3.3897097588576198E-17</v>
@@ -1293,7 +1295,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8">
         <v>26896</v>
@@ -1302,7 +1304,7 @@
         <v>31494</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E8" s="1">
         <v>7.2645676168526097E-16</v>
@@ -1322,7 +1324,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B9">
         <v>26896</v>
@@ -1331,7 +1333,7 @@
         <v>31494</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E9" s="1">
         <v>4.95081966335702E-13</v>
@@ -1351,7 +1353,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10">
         <v>26896</v>
@@ -1360,7 +1362,7 @@
         <v>31494</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E10" s="1">
         <v>1.9919496694187802E-12</v>
@@ -1380,7 +1382,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>26896</v>
@@ -1389,7 +1391,7 @@
         <v>31494</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E11" s="1">
         <v>1.5739650524621299E-7</v>
@@ -1409,7 +1411,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B12">
         <v>26896</v>
@@ -1418,7 +1420,7 @@
         <v>31494</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E12" s="1">
         <v>9.1448904080669898E-7</v>
@@ -1438,7 +1440,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B13">
         <v>26896</v>
@@ -1447,7 +1449,7 @@
         <v>31494</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E13" s="1">
         <v>3.25016758382173E-6</v>
@@ -1467,7 +1469,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B14">
         <v>26896</v>
@@ -1476,7 +1478,7 @@
         <v>31494</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E14">
         <v>1.0094697712793001E-4</v>
@@ -1496,7 +1498,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B15">
         <v>26896</v>
@@ -1505,7 +1507,7 @@
         <v>31494</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E15">
         <v>1.08668382750858E-4</v>
@@ -1525,7 +1527,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B16">
         <v>26896</v>
@@ -1534,7 +1536,7 @@
         <v>31494</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E16">
         <v>2.39623446755206E-4</v>
@@ -1554,7 +1556,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B17">
         <v>26896</v>
@@ -1563,7 +1565,7 @@
         <v>31494</v>
       </c>
       <c r="D17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E17">
         <v>5.9688904536946705E-4</v>
@@ -1583,7 +1585,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B18">
         <v>26896</v>
@@ -1592,7 +1594,7 @@
         <v>31494</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E18">
         <v>5.6199040711329501E-2</v>
@@ -1612,7 +1614,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B19">
         <v>26896</v>
@@ -1621,7 +1623,7 @@
         <v>31494</v>
       </c>
       <c r="D19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E19">
         <v>0.379135674904994</v>
@@ -1641,7 +1643,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B20">
         <v>31245</v>
@@ -1650,7 +1652,7 @@
         <v>42753</v>
       </c>
       <c r="D20" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E20" s="1">
         <v>3.2662276213365202E-25</v>
@@ -1670,7 +1672,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B21">
         <v>31245</v>
@@ -1679,7 +1681,7 @@
         <v>42753</v>
       </c>
       <c r="D21" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E21" s="1">
         <v>2.04031662950683E-10</v>
@@ -1699,7 +1701,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B22">
         <v>31245</v>
@@ -1708,7 +1710,7 @@
         <v>42753</v>
       </c>
       <c r="D22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E22" s="1">
         <v>5.64863501554212E-9</v>
@@ -1728,7 +1730,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B23">
         <v>31245</v>
@@ -1737,7 +1739,7 @@
         <v>42753</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E23" s="1">
         <v>9.7822677872094993E-7</v>
@@ -1757,7 +1759,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B24">
         <v>31245</v>
@@ -1766,7 +1768,7 @@
         <v>42753</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E24" s="1">
         <v>3.2350671519126397E-5</v>
@@ -1786,7 +1788,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B25">
         <v>31245</v>
@@ -1795,7 +1797,7 @@
         <v>42753</v>
       </c>
       <c r="D25" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E25">
         <v>8.1079968315119497E-4</v>
@@ -1815,7 +1817,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B26">
         <v>31245</v>
@@ -1824,7 +1826,7 @@
         <v>42753</v>
       </c>
       <c r="D26" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E26">
         <v>1.00569543580591E-3</v>
@@ -1844,7 +1846,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B27">
         <v>31245</v>
@@ -1853,7 +1855,7 @@
         <v>42753</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E27">
         <v>2.14975923777789E-3</v>
@@ -1873,7 +1875,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B28">
         <v>31245</v>
@@ -1882,7 +1884,7 @@
         <v>42753</v>
       </c>
       <c r="D28" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E28">
         <v>5.5453233363115997E-3</v>
@@ -1902,7 +1904,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B29">
         <v>31245</v>
@@ -1911,7 +1913,7 @@
         <v>42753</v>
       </c>
       <c r="D29" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E29">
         <v>5.9523607912306403E-3</v>
@@ -1931,7 +1933,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B30">
         <v>31245</v>
@@ -1940,7 +1942,7 @@
         <v>42753</v>
       </c>
       <c r="D30" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E30">
         <v>1.86084839726646E-2</v>
@@ -1960,7 +1962,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B31">
         <v>31245</v>
@@ -1969,7 +1971,7 @@
         <v>42753</v>
       </c>
       <c r="D31" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E31">
         <v>3.6415945383619898E-2</v>
@@ -1989,7 +1991,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B32">
         <v>31245</v>
@@ -1998,7 +2000,7 @@
         <v>42753</v>
       </c>
       <c r="D32" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E32">
         <v>5.25091843292095E-2</v>
@@ -2018,7 +2020,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B33">
         <v>31245</v>
@@ -2027,7 +2029,7 @@
         <v>42753</v>
       </c>
       <c r="D33" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E33">
         <v>0.15181094926255101</v>
@@ -2047,7 +2049,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B34">
         <v>31245</v>
@@ -2056,7 +2058,7 @@
         <v>42753</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E34">
         <v>0.320339662267561</v>
@@ -2076,7 +2078,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B35">
         <v>31245</v>
@@ -2085,7 +2087,7 @@
         <v>42753</v>
       </c>
       <c r="D35" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E35">
         <v>0.67551094128537503</v>
@@ -2105,7 +2107,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B36">
         <v>31245</v>
@@ -2114,7 +2116,7 @@
         <v>42753</v>
       </c>
       <c r="D36" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E36">
         <v>0.67648740658859197</v>
@@ -2134,7 +2136,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B37">
         <v>31245</v>
@@ -2143,7 +2145,7 @@
         <v>42753</v>
       </c>
       <c r="D37" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E37">
         <v>0.98949658036755705</v>
@@ -2163,7 +2165,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B38">
         <v>9388</v>
@@ -2172,7 +2174,7 @@
         <v>12032</v>
       </c>
       <c r="D38" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E38" s="1">
         <v>3.0751643138105599E-15</v>
@@ -2192,7 +2194,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B39">
         <v>9388</v>
@@ -2201,7 +2203,7 @@
         <v>12032</v>
       </c>
       <c r="D39" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E39" s="1">
         <v>7.3562833405855496E-13</v>
@@ -2221,7 +2223,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B40">
         <v>9388</v>
@@ -2230,7 +2232,7 @@
         <v>12032</v>
       </c>
       <c r="D40" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E40" s="1">
         <v>2.26276872532325E-11</v>
@@ -2250,7 +2252,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B41">
         <v>9388</v>
@@ -2259,7 +2261,7 @@
         <v>12032</v>
       </c>
       <c r="D41" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E41" s="1">
         <v>4.3886119306332402E-10</v>
@@ -2279,7 +2281,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B42">
         <v>9388</v>
@@ -2288,7 +2290,7 @@
         <v>12032</v>
       </c>
       <c r="D42" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E42" s="1">
         <v>6.3479326894360505E-5</v>
@@ -2308,7 +2310,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B43">
         <v>9388</v>
@@ -2317,7 +2319,7 @@
         <v>12032</v>
       </c>
       <c r="D43" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E43">
         <v>1.0567554125068E-4</v>
@@ -2337,7 +2339,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B44">
         <v>9388</v>
@@ -2346,7 +2348,7 @@
         <v>12032</v>
       </c>
       <c r="D44" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E44">
         <v>1.3430322851186601E-3</v>
@@ -2366,7 +2368,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B45">
         <v>9388</v>
@@ -2375,7 +2377,7 @@
         <v>12032</v>
       </c>
       <c r="D45" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E45">
         <v>2.5759724826745298E-3</v>
@@ -2395,7 +2397,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B46">
         <v>9388</v>
@@ -2404,7 +2406,7 @@
         <v>12032</v>
       </c>
       <c r="D46" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E46">
         <v>2.8165158957404301E-3</v>
@@ -2424,7 +2426,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B47">
         <v>9388</v>
@@ -2433,7 +2435,7 @@
         <v>12032</v>
       </c>
       <c r="D47" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E47">
         <v>1.0200848223838601E-2</v>
@@ -2453,7 +2455,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B48">
         <v>9388</v>
@@ -2462,7 +2464,7 @@
         <v>12032</v>
       </c>
       <c r="D48" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E48">
         <v>1.7045831360250101E-2</v>
@@ -2482,7 +2484,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B49">
         <v>9388</v>
@@ -2491,7 +2493,7 @@
         <v>12032</v>
       </c>
       <c r="D49" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E49">
         <v>3.3904396034084003E-2</v>
@@ -2511,7 +2513,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B50">
         <v>9388</v>
@@ -2520,7 +2522,7 @@
         <v>12032</v>
       </c>
       <c r="D50" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E50">
         <v>6.2507384590012302E-2</v>
@@ -2540,7 +2542,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B51">
         <v>9388</v>
@@ -2549,7 +2551,7 @@
         <v>12032</v>
       </c>
       <c r="D51" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E51">
         <v>0.121785663438368</v>
@@ -2569,7 +2571,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B52">
         <v>9388</v>
@@ -2578,7 +2580,7 @@
         <v>12032</v>
       </c>
       <c r="D52" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E52">
         <v>0.13093964450345699</v>
@@ -2598,7 +2600,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B53">
         <v>9388</v>
@@ -2607,7 +2609,7 @@
         <v>12032</v>
       </c>
       <c r="D53" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E53">
         <v>0.41933262656865999</v>
@@ -2627,7 +2629,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B54">
         <v>9388</v>
@@ -2636,7 +2638,7 @@
         <v>12032</v>
       </c>
       <c r="D54" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E54">
         <v>0.76770338986323505</v>
@@ -2656,7 +2658,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B55">
         <v>9388</v>
@@ -2665,7 +2667,7 @@
         <v>12032</v>
       </c>
       <c r="D55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E55">
         <v>0.92789925331302403</v>
@@ -2685,7 +2687,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B56">
         <v>12254</v>
@@ -2694,7 +2696,7 @@
         <v>15060</v>
       </c>
       <c r="D56" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E56" s="1">
         <v>4.06785792966859E-34</v>
@@ -2714,7 +2716,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B57">
         <v>12254</v>
@@ -2723,7 +2725,7 @@
         <v>15060</v>
       </c>
       <c r="D57" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E57" s="1">
         <v>1.5480062303535099E-14</v>
@@ -2743,7 +2745,7 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B58">
         <v>12254</v>
@@ -2752,7 +2754,7 @@
         <v>15060</v>
       </c>
       <c r="D58" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E58" s="1">
         <v>2.0305885226254398E-14</v>
@@ -2772,7 +2774,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B59">
         <v>12254</v>
@@ -2781,7 +2783,7 @@
         <v>15060</v>
       </c>
       <c r="D59" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E59" s="1">
         <v>4.0624755895670902E-12</v>
@@ -2801,7 +2803,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B60">
         <v>12254</v>
@@ -2810,7 +2812,7 @@
         <v>15060</v>
       </c>
       <c r="D60" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E60" s="1">
         <v>4.1768356057105602E-12</v>
@@ -2830,7 +2832,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B61">
         <v>12254</v>
@@ -2839,7 +2841,7 @@
         <v>15060</v>
       </c>
       <c r="D61" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E61" s="1">
         <v>6.7441277487718506E-11</v>
@@ -2859,7 +2861,7 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B62">
         <v>12254</v>
@@ -2868,7 +2870,7 @@
         <v>15060</v>
       </c>
       <c r="D62" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E62" s="1">
         <v>7.4178078874727105E-10</v>
@@ -2888,7 +2890,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B63">
         <v>12254</v>
@@ -2897,7 +2899,7 @@
         <v>15060</v>
       </c>
       <c r="D63" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E63" s="1">
         <v>2.4111748504538301E-9</v>
@@ -2917,7 +2919,7 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B64">
         <v>12254</v>
@@ -2926,7 +2928,7 @@
         <v>15060</v>
       </c>
       <c r="D64" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E64" s="1">
         <v>2.5000922989952401E-8</v>
@@ -2946,7 +2948,7 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B65">
         <v>12254</v>
@@ -2955,7 +2957,7 @@
         <v>15060</v>
       </c>
       <c r="D65" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E65" s="1">
         <v>2.0425794220533699E-7</v>
@@ -2975,7 +2977,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B66">
         <v>12254</v>
@@ -2984,7 +2986,7 @@
         <v>15060</v>
       </c>
       <c r="D66" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E66" s="1">
         <v>1.21359696144249E-6</v>
@@ -3004,7 +3006,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B67">
         <v>12254</v>
@@ -3013,7 +3015,7 @@
         <v>15060</v>
       </c>
       <c r="D67" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E67" s="1">
         <v>2.5233627689886699E-6</v>
@@ -3033,7 +3035,7 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B68">
         <v>12254</v>
@@ -3042,7 +3044,7 @@
         <v>15060</v>
       </c>
       <c r="D68" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E68" s="1">
         <v>4.9203022466126801E-6</v>
@@ -3062,7 +3064,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B69">
         <v>12254</v>
@@ -3071,7 +3073,7 @@
         <v>15060</v>
       </c>
       <c r="D69" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E69" s="1">
         <v>3.1500537562620197E-5</v>
@@ -3091,7 +3093,7 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B70">
         <v>12254</v>
@@ -3100,7 +3102,7 @@
         <v>15060</v>
       </c>
       <c r="D70" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E70">
         <v>7.36914269022106E-4</v>
@@ -3120,7 +3122,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B71">
         <v>12254</v>
@@ -3129,7 +3131,7 @@
         <v>15060</v>
       </c>
       <c r="D71" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E71">
         <v>5.3925311758353002E-3</v>
@@ -3149,7 +3151,7 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B72">
         <v>12254</v>
@@ -3158,7 +3160,7 @@
         <v>15060</v>
       </c>
       <c r="D72" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E72">
         <v>2.45359028469051E-2</v>
@@ -3178,7 +3180,7 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B73">
         <v>12254</v>
@@ -3187,7 +3189,7 @@
         <v>15060</v>
       </c>
       <c r="D73" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E73">
         <v>6.4135370761199295E-2</v>
@@ -3207,7 +3209,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B74">
         <v>732</v>
@@ -3216,7 +3218,7 @@
         <v>1884</v>
       </c>
       <c r="D74" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E74">
         <v>1.6985505547874501E-2</v>
@@ -3236,7 +3238,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B75">
         <v>732</v>
@@ -3245,7 +3247,7 @@
         <v>1884</v>
       </c>
       <c r="D75" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E75">
         <v>3.5209175045461803E-2</v>
@@ -3265,7 +3267,7 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B76">
         <v>732</v>
@@ -3274,7 +3276,7 @@
         <v>1884</v>
       </c>
       <c r="D76" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E76">
         <v>9.1326686897276799E-2</v>
@@ -3294,7 +3296,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B77">
         <v>732</v>
@@ -3303,7 +3305,7 @@
         <v>1884</v>
       </c>
       <c r="D77" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E77">
         <v>9.6986675004080897E-2</v>
@@ -3323,7 +3325,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B78">
         <v>732</v>
@@ -3332,7 +3334,7 @@
         <v>1884</v>
       </c>
       <c r="D78" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E78">
         <v>0.10880928085548799</v>
@@ -3352,7 +3354,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B79">
         <v>732</v>
@@ -3361,7 +3363,7 @@
         <v>1884</v>
       </c>
       <c r="D79" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E79">
         <v>0.124175669480838</v>
@@ -3381,7 +3383,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B80">
         <v>732</v>
@@ -3390,7 +3392,7 @@
         <v>1884</v>
       </c>
       <c r="D80" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E80">
         <v>0.13862907987175599</v>
@@ -3410,7 +3412,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B81">
         <v>732</v>
@@ -3419,7 +3421,7 @@
         <v>1884</v>
       </c>
       <c r="D81" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E81">
         <v>0.147202214228594</v>
@@ -3439,7 +3441,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B82">
         <v>732</v>
@@ -3448,7 +3450,7 @@
         <v>1884</v>
       </c>
       <c r="D82" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E82">
         <v>0.22448855247600399</v>
@@ -3468,7 +3470,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B83">
         <v>732</v>
@@ -3477,7 +3479,7 @@
         <v>1884</v>
       </c>
       <c r="D83" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E83">
         <v>0.339424290188374</v>
@@ -3497,7 +3499,7 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B84">
         <v>732</v>
@@ -3506,7 +3508,7 @@
         <v>1884</v>
       </c>
       <c r="D84" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E84">
         <v>0.47400837346966301</v>
@@ -3526,7 +3528,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B85">
         <v>732</v>
@@ -3535,7 +3537,7 @@
         <v>1884</v>
       </c>
       <c r="D85" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E85">
         <v>0.51943791478551404</v>
@@ -3555,7 +3557,7 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B86">
         <v>732</v>
@@ -3564,7 +3566,7 @@
         <v>1884</v>
       </c>
       <c r="D86" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E86">
         <v>0.58552061587757898</v>
@@ -3584,7 +3586,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B87">
         <v>732</v>
@@ -3593,7 +3595,7 @@
         <v>1884</v>
       </c>
       <c r="D87" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E87">
         <v>0.66747942662578397</v>
@@ -3613,7 +3615,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B88">
         <v>732</v>
@@ -3622,7 +3624,7 @@
         <v>1884</v>
       </c>
       <c r="D88" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E88">
         <v>0.74030696449728595</v>
@@ -3642,7 +3644,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B89">
         <v>4346</v>
@@ -3651,7 +3653,7 @@
         <v>6060</v>
       </c>
       <c r="D89" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E89" s="1">
         <v>2.76368553690486E-10</v>
@@ -3671,7 +3673,7 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B90">
         <v>4346</v>
@@ -3680,7 +3682,7 @@
         <v>6060</v>
       </c>
       <c r="D90" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E90" s="1">
         <v>3.0993426512567402E-10</v>
@@ -3700,7 +3702,7 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B91">
         <v>4346</v>
@@ -3709,7 +3711,7 @@
         <v>6060</v>
       </c>
       <c r="D91" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E91" s="1">
         <v>5.2795496219297997E-10</v>
@@ -3729,7 +3731,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B92">
         <v>4346</v>
@@ -3738,7 +3740,7 @@
         <v>6060</v>
       </c>
       <c r="D92" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E92" s="1">
         <v>9.5079395380537906E-10</v>
@@ -3758,7 +3760,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B93">
         <v>4346</v>
@@ -3767,7 +3769,7 @@
         <v>6060</v>
       </c>
       <c r="D93" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E93" s="1">
         <v>2.5380498196729599E-8</v>
@@ -3787,7 +3789,7 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B94">
         <v>4346</v>
@@ -3796,7 +3798,7 @@
         <v>6060</v>
       </c>
       <c r="D94" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E94" s="1">
         <v>2.5880826359590801E-8</v>
@@ -3816,7 +3818,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B95">
         <v>4346</v>
@@ -3825,7 +3827,7 @@
         <v>6060</v>
       </c>
       <c r="D95" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E95" s="1">
         <v>4.0943919613195999E-8</v>
@@ -3845,7 +3847,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B96">
         <v>4346</v>
@@ -3854,7 +3856,7 @@
         <v>6060</v>
       </c>
       <c r="D96" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E96">
         <v>1.3204028435702999E-4</v>
@@ -3874,7 +3876,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B97">
         <v>4346</v>
@@ -3883,7 +3885,7 @@
         <v>6060</v>
       </c>
       <c r="D97" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E97">
         <v>1.3782234623208701E-4</v>
@@ -3903,7 +3905,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B98">
         <v>4346</v>
@@ -3912,7 +3914,7 @@
         <v>6060</v>
       </c>
       <c r="D98" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E98">
         <v>6.4355663158772796E-4</v>
@@ -3932,7 +3934,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B99">
         <v>4346</v>
@@ -3941,7 +3943,7 @@
         <v>6060</v>
       </c>
       <c r="D99" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E99">
         <v>7.6398152015323098E-4</v>
@@ -3961,7 +3963,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B100">
         <v>4346</v>
@@ -3970,7 +3972,7 @@
         <v>6060</v>
       </c>
       <c r="D100" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E100">
         <v>2.8048612879300202E-3</v>
@@ -3990,7 +3992,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B101">
         <v>4346</v>
@@ -3999,7 +4001,7 @@
         <v>6060</v>
       </c>
       <c r="D101" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E101">
         <v>4.8567204025990801E-3</v>
@@ -4019,7 +4021,7 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B102">
         <v>4346</v>
@@ -4028,7 +4030,7 @@
         <v>6060</v>
       </c>
       <c r="D102" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E102">
         <v>8.5211568497130605E-3</v>
@@ -4048,7 +4050,7 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B103">
         <v>4346</v>
@@ -4057,7 +4059,7 @@
         <v>6060</v>
       </c>
       <c r="D103" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E103">
         <v>3.7368656345012199E-2</v>
@@ -4077,7 +4079,7 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B104">
         <v>4346</v>
@@ -4086,7 +4088,7 @@
         <v>6060</v>
       </c>
       <c r="D104" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E104">
         <v>8.0046618884618198E-2</v>
@@ -4106,7 +4108,7 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B105">
         <v>5911</v>
@@ -4115,7 +4117,7 @@
         <v>6954</v>
       </c>
       <c r="D105" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E105" s="1">
         <v>6.8836403105168501E-7</v>
@@ -4135,7 +4137,7 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B106">
         <v>5911</v>
@@ -4144,7 +4146,7 @@
         <v>6954</v>
       </c>
       <c r="D106" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E106" s="1">
         <v>1.8595758203010901E-5</v>
@@ -4164,7 +4166,7 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B107">
         <v>5911</v>
@@ -4173,7 +4175,7 @@
         <v>6954</v>
       </c>
       <c r="D107" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E107" s="1">
         <v>5.12333069326698E-5</v>
@@ -4193,7 +4195,7 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B108">
         <v>5911</v>
@@ -4202,7 +4204,7 @@
         <v>6954</v>
       </c>
       <c r="D108" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E108" s="1">
         <v>8.0023111818269097E-5</v>
@@ -4222,7 +4224,7 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B109">
         <v>5911</v>
@@ -4231,7 +4233,7 @@
         <v>6954</v>
       </c>
       <c r="D109" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E109">
         <v>1.65996230601425E-3</v>
@@ -4251,7 +4253,7 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B110">
         <v>5911</v>
@@ -4260,7 +4262,7 @@
         <v>6954</v>
       </c>
       <c r="D110" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E110">
         <v>5.7344289466179296E-3</v>
@@ -4280,7 +4282,7 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B111">
         <v>5911</v>
@@ -4289,7 +4291,7 @@
         <v>6954</v>
       </c>
       <c r="D111" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E111">
         <v>6.3716602770571302E-3</v>
@@ -4309,7 +4311,7 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B112">
         <v>5911</v>
@@ -4318,7 +4320,7 @@
         <v>6954</v>
       </c>
       <c r="D112" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E112">
         <v>2.28887402246544E-2</v>
@@ -4338,7 +4340,7 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B113">
         <v>5911</v>
@@ -4347,7 +4349,7 @@
         <v>6954</v>
       </c>
       <c r="D113" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E113">
         <v>3.7986148821367603E-2</v>
@@ -4367,7 +4369,7 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B114">
         <v>5911</v>
@@ -4376,7 +4378,7 @@
         <v>6954</v>
       </c>
       <c r="D114" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E114">
         <v>5.05218708698549E-2</v>
@@ -4396,7 +4398,7 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B115">
         <v>5911</v>
@@ -4405,7 +4407,7 @@
         <v>6954</v>
       </c>
       <c r="D115" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E115">
         <v>6.7431525880861598E-2</v>
@@ -4425,7 +4427,7 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B116">
         <v>5911</v>
@@ -4434,7 +4436,7 @@
         <v>6954</v>
       </c>
       <c r="D116" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E116">
         <v>0.10205786805491</v>
@@ -4454,7 +4456,7 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B117">
         <v>5911</v>
@@ -4463,7 +4465,7 @@
         <v>6954</v>
       </c>
       <c r="D117" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E117">
         <v>0.172715508547787</v>
@@ -4483,7 +4485,7 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B118">
         <v>5911</v>
@@ -4492,7 +4494,7 @@
         <v>6954</v>
       </c>
       <c r="D118" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E118">
         <v>0.187939841289087</v>
@@ -4512,7 +4514,7 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B119">
         <v>5911</v>
@@ -4521,7 +4523,7 @@
         <v>6954</v>
       </c>
       <c r="D119" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E119">
         <v>0.20186492267951101</v>
@@ -4541,7 +4543,7 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B120">
         <v>5911</v>
@@ -4550,7 +4552,7 @@
         <v>6954</v>
       </c>
       <c r="D120" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E120">
         <v>0.58330115899629997</v>
@@ -4570,7 +4572,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B121">
         <v>5911</v>
@@ -4579,7 +4581,7 @@
         <v>6954</v>
       </c>
       <c r="D121" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E121">
         <v>0.61634595582571905</v>
@@ -4599,7 +4601,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B122">
         <v>5911</v>
@@ -4608,7 +4610,7 @@
         <v>6954</v>
       </c>
       <c r="D122" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E122">
         <v>0.64515328621739998</v>
@@ -4628,7 +4630,7 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B123">
         <v>90772</v>
@@ -4637,7 +4639,7 @@
         <v>116237</v>
       </c>
       <c r="D123" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E123" s="1">
         <v>3.3145399178694901E-63</v>
@@ -4657,7 +4659,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B124">
         <v>90772</v>
@@ -4666,7 +4668,7 @@
         <v>116237</v>
       </c>
       <c r="D124" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E124" s="1">
         <v>1.5304792686315799E-59</v>
@@ -4686,7 +4688,7 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B125">
         <v>90772</v>
@@ -4695,7 +4697,7 @@
         <v>116237</v>
       </c>
       <c r="D125" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E125" s="1">
         <v>1.1374701575428199E-43</v>
@@ -4715,7 +4717,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B126">
         <v>90772</v>
@@ -4724,7 +4726,7 @@
         <v>116237</v>
       </c>
       <c r="D126" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E126" s="1">
         <v>1.41991719061167E-33</v>
@@ -4744,7 +4746,7 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B127">
         <v>90772</v>
@@ -4753,7 +4755,7 @@
         <v>116237</v>
       </c>
       <c r="D127" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E127" s="1">
         <v>2.15611898017391E-33</v>
@@ -4773,7 +4775,7 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B128">
         <v>90772</v>
@@ -4782,7 +4784,7 @@
         <v>116237</v>
       </c>
       <c r="D128" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E128" s="1">
         <v>3.6018953392931301E-22</v>
@@ -4802,7 +4804,7 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B129">
         <v>90772</v>
@@ -4811,7 +4813,7 @@
         <v>116237</v>
       </c>
       <c r="D129" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E129" s="1">
         <v>2.98214603623879E-19</v>
@@ -4831,7 +4833,7 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B130">
         <v>90772</v>
@@ -4840,7 +4842,7 @@
         <v>116237</v>
       </c>
       <c r="D130" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E130" s="1">
         <v>5.7034408502062296E-16</v>
@@ -4860,7 +4862,7 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B131">
         <v>90772</v>
@@ -4869,7 +4871,7 @@
         <v>116237</v>
       </c>
       <c r="D131" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E131" s="1">
         <v>5.2993903491423401E-14</v>
@@ -4889,7 +4891,7 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B132">
         <v>90772</v>
@@ -4898,7 +4900,7 @@
         <v>116237</v>
       </c>
       <c r="D132" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E132" s="1">
         <v>2.7659222965218101E-11</v>
@@ -4918,7 +4920,7 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B133">
         <v>90772</v>
@@ -4927,7 +4929,7 @@
         <v>116237</v>
       </c>
       <c r="D133" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E133" s="1">
         <v>4.26975980932419E-11</v>
@@ -4947,7 +4949,7 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B134">
         <v>90772</v>
@@ -4956,7 +4958,7 @@
         <v>116237</v>
       </c>
       <c r="D134" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E134" s="1">
         <v>1.4020244283303401E-6</v>
@@ -4976,7 +4978,7 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B135">
         <v>90772</v>
@@ -4985,7 +4987,7 @@
         <v>116237</v>
       </c>
       <c r="D135" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E135" s="1">
         <v>3.56201901693262E-6</v>
@@ -5005,7 +5007,7 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B136">
         <v>90772</v>
@@ -5014,7 +5016,7 @@
         <v>116237</v>
       </c>
       <c r="D136" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E136" s="1">
         <v>3.2425370996188003E-5</v>
@@ -5034,7 +5036,7 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B137">
         <v>90772</v>
@@ -5043,7 +5045,7 @@
         <v>116237</v>
       </c>
       <c r="D137" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E137" s="1">
         <v>3.81703475645295E-5</v>
@@ -5063,7 +5065,7 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B138">
         <v>90772</v>
@@ -5072,7 +5074,7 @@
         <v>116237</v>
       </c>
       <c r="D138" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E138">
         <v>1.2554151777027E-2</v>
@@ -5092,7 +5094,7 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B139">
         <v>90772</v>
@@ -5101,7 +5103,7 @@
         <v>116237</v>
       </c>
       <c r="D139" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E139">
         <v>4.91729591587148E-2</v>
@@ -5121,7 +5123,7 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B140">
         <v>90772</v>
@@ -5130,7 +5132,7 @@
         <v>116237</v>
       </c>
       <c r="D140" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E140">
         <v>6.2676716740152502E-2</v>
